--- a/Resource/丝印表单集.xlsx
+++ b/Resource/丝印表单集.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ShiJD\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04-ProjectFile-LineControl\v0\resource\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA5B0D6-6B55-4840-BB76-685D7D453738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E096316B-13CD-4B7B-ACC7-FCF88BEE6DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-260" yWindow="0" windowWidth="14030" windowHeight="13770" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14740" yWindow="1100" windowWidth="24800" windowHeight="12290" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="用户输入" sheetId="1" r:id="rId1"/>
-    <sheet name="生产规划" sheetId="2" r:id="rId2"/>
-    <sheet name="生产执行" sheetId="3" r:id="rId3"/>
+    <sheet name="V0_用户输入V0" sheetId="1" r:id="rId1"/>
+    <sheet name="V-_生产规划" sheetId="2" r:id="rId2"/>
+    <sheet name="V0_生产执行" sheetId="3" r:id="rId3"/>
+    <sheet name="V1_用户输入" sheetId="4" r:id="rId4"/>
+    <sheet name="V1_工艺规划" sheetId="6" r:id="rId5"/>
+    <sheet name="V1_生产指令" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">用户输入!$B$2:$C$13</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">用户输入!1:3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">V0_用户输入V0!$B$2:$C$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">V0_用户输入V0!1:3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="111">
   <si>
     <t>运动鞋面生产任务表</t>
   </si>
@@ -87,10 +90,6 @@
   </si>
   <si>
     <t>神行橘</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>34-35</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -122,10 +121,6 @@
   </si>
   <si>
     <t>日期：2025年10月30日</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>工序清单</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -223,12 +218,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1. 将网版1装入丝印工作站1，并填入5kg胶浆
-2. 将网版2装入丝印工作站2，并填入2kg橘红色油墨
-3. 将网版3装入丝印工作站3，并填入2kg深红色油墨</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>人员准备</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -281,6 +270,304 @@
   </si>
   <si>
     <t>指令序列</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>质量要求</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>42-43</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>面料厚度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>材质</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>网布</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2mm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工序流程</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 油墨胶浆
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   -处理剂: 0.5kg 临昊打底剂 + 5%硬化剂
+   -胶浆: 5kg 临昊打底树脂 + 3%硬化剂
+   -橘红油墨（色号：x#）: 2kg
+   -深红油墨（色号：x#）: 2kg
+   -哑光白油墨（色号：x#）：2kg
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2. 网版制作
+   -网版1（ID，设计文件，线径，孔径，张力）
+   -网版2（ID，设计文件，线径，孔径，张力）
+   -网版3（ID，设计文件，线径，孔径，张力）
+3. 面料准备</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 将网版1装入丝印工作站1，并填入5kg胶浆
+2. 将网版2装入丝印工作站2，并填入2kg橘红色油墨
+3. 将网版3装入丝印工作站3，并填入2kg深红色油墨
+4. 装填物料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>层厚，色牢度，耐折次数，耐水洗</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>厚度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶浆层厚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2mm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>运动鞋面生产任务单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>色牢度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>干摩 &gt; 4; 湿摩 &gt; 3.5; 水 &gt;= 3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐折次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>水洗后尺寸变化</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;1%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图案设计</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>网版准备指令</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>胶浆油墨准备指令</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人：张三（技工）
+1. 制作网版1：ID, 设计文件，线径，目数，张力
+2. 制作网版2：ID, 设计文件，线径，目数，张力
+3. 制作网版3：ID, 设计文件，线径，目数，张力</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人：王五（普工）
+1. 将网版1装入丝印工作站1，并填入5kg胶浆
+2. 将网版2装入丝印工作站2，并填入2kg橘红色油墨
+3. 将网版3装入丝印工作站3，并填入2kg深红色油墨
+4. 装填物料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>设备准备指令</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产准备指令单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上料准备</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产指令单编号：13524</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产执行指令单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产执行编号：13524</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">任务类型：xxx
+任务描述：xxx
+。。。
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>上料工作站指令</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作站1：刮刀角度：xxx 。。。
+工作站2：刮刀角度：xxx 。。。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝印工作站参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>烘干参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">烘干工作站 1：温度：xxx，时间：yyy
+烘干工作站 2：温度：xxx，时间：yyy
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>线体参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度：10 km / hr</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人：李四（技工）
+1. 处理剂: 0.5kg 临昊打底剂 + 5%硬化剂
+2. 胶浆: 5kg 临昊打底树脂 + 3%硬化剂
+3. 橘红油墨（色号：x#）: 2kg
+4. 深红油墨（色号：x#）: 2kg
+5. 哑光白油墨（色号：x#）：2kg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>负责人：王五（普工）
+1. 在仓库1准备100片面料A
+2. 在仓库2准备100片面料A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>网版设计方案</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工序流程单</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>方案编号：12312</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期：2025/11/17</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>层序号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>图案：X
+张力：Y
+目数：Z
+线径：A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝印参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>角度: X
+速度: Y
+间距: Z
+…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版1胶浆打底（厚度:2mm）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版0涂抹处理剂（厚度:0.5mm）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版2上深红色(0.5mm)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>工序编号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版0涂抹处理剂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版1胶浆打底</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用网版2上深红色</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>裁片A 100片</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>油墨A 10 KG</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -291,7 +578,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,16 +607,43 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -453,11 +767,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -486,33 +815,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -537,13 +912,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>374651</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>4152900</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>2501319</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -575,6 +950,61 @@
         <a:xfrm>
           <a:off x="2921000" y="4813301"/>
           <a:ext cx="3797300" cy="2126668"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1206500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>172415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>4394200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>2539418</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BFABD8E-4B02-4C9A-95A9-E031E9965DB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3416300" y="5303215"/>
+          <a:ext cx="3187700" cy="2367003"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -871,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:C12"/>
+  <dimension ref="B1:C15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -880,22 +1310,22 @@
   <sheetData>
     <row r="1" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="52" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
@@ -938,29 +1368,53 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C12" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="228" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+    <row r="13" spans="2:3" ht="300.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="2:3" ht="54.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="8" t="s">
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="54.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
+      <c r="C15" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -972,7 +1426,7 @@
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>DATE(2000,1,1)</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -993,22 +1447,22 @@
   <sheetData>
     <row r="1" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="46" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="11"/>
+      <c r="B2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
@@ -1016,54 +1470,54 @@
     </row>
     <row r="5" spans="2:3" ht="84" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>26</v>
+        <v>58</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="42" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="112" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>27</v>
+        <v>22</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="2:3" ht="54.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="11"/>
+      <c r="B11" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="20"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>8</v>
@@ -1071,34 +1525,34 @@
     </row>
     <row r="14" spans="2:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="56" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>37</v>
+        <v>31</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1122,69 +1576,69 @@
   <sheetData>
     <row r="1" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:3" ht="67" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="11"/>
+      <c r="B2" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" spans="2:3" ht="28" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:3" ht="15" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="112" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="154" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="42" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="56" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>41</v>
+        <v>37</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="28.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:3" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="11"/>
+      <c r="B10" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20"/>
     </row>
     <row r="11" spans="2:3" ht="28" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>8</v>
@@ -1194,7 +1648,7 @@
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1202,48 +1656,48 @@
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="16">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="18" t="s">
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="18">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>49</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1254,4 +1708,631 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B227F40-E8A4-4B2A-8EE9-C2BAC34348E5}">
+  <dimension ref="B11:C27"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.90625" customWidth="1"/>
+    <col min="3" max="3" width="76.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="11" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="20"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="226" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B12:C12"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{A8A92724-8600-4848-A74A-0AEBFFB8113F}">
+      <formula1>DATE(2000,1,1)</formula1>
+    </dataValidation>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C26" xr:uid="{0670257A-5758-4095-97AA-F85AA844BC44}"/>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B532AEB3-67C1-40C3-98FE-EA3E5F073A1C}">
+  <dimension ref="B1:C53"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="46.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:3" ht="52" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="29"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B5" s="31">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B6" s="31">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="32">
+        <v>2</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+    </row>
+    <row r="9" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:3" ht="66.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="29"/>
+    </row>
+    <row r="11" spans="2:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B13" s="31">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B14" s="31">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="32">
+        <v>2</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="34"/>
+      <c r="C16" s="35"/>
+    </row>
+    <row r="17" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+    </row>
+    <row r="18" spans="2:3" ht="51.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="29"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B21" s="31">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B22" s="31">
+        <v>1</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="56.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="32">
+        <v>2</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="B26" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="29"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="31">
+        <v>1</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="31">
+        <v>2</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="32">
+        <v>3</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="2:3" ht="40" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C34" s="29"/>
+    </row>
+    <row r="35" spans="2:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="33.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="31">
+        <v>1</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="31">
+        <v>2</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="32">
+        <v>3</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="B42" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="29"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="31">
+        <v>1</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="32">
+        <v>2</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="2:3" ht="23" x14ac:dyDescent="0.25">
+      <c r="B49" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="29"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="31">
+        <v>1</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="32">
+        <v>2</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B10:C10"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{855A54AE-CFAF-4BD5-B4DD-39AEF53B9690}">
+  <dimension ref="B1:C17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:3" ht="49" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="20"/>
+    </row>
+    <row r="3" spans="2:3" ht="42" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="84" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="70" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" ht="42.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="2:3" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="20"/>
+    </row>
+    <row r="12" spans="2:3" ht="42" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" ht="56" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" ht="28" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" ht="42" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B11:C11"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>